--- a/data.xlsx
+++ b/data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allegiscloud-my.sharepoint.com/personal/mbaweja_teksystems_com1/Documents/Desktop/Git Page COE/mehak1996.github.io/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46149DD0-83B5-4720-9809-BBBBB8C6A7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{46149DD0-83B5-4720-9809-BBBBB8C6A7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68F60A7C-1DC0-4C22-876D-5EC5D50A4287}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{6EC15607-7297-42CE-928E-0DBAFFD9E6D8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="mapping" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +35,80 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+  <si>
+    <t>Columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mapping Information </t>
+  </si>
+  <si>
+    <t>sourceId</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>MDM_ID</t>
+  </si>
+  <si>
+    <t>serviceClass</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>accountType</t>
+  </si>
+  <si>
+    <t>AdministrativeContactFlag</t>
+  </si>
+  <si>
+    <t>JobTitle</t>
+  </si>
+  <si>
+    <t>SupplierInactiveDate</t>
+  </si>
+  <si>
+    <t>SupplierStatus</t>
+  </si>
+  <si>
+    <t>ContactInactiveDate</t>
+  </si>
+  <si>
+    <t>ContactStatus</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>CountryCode</t>
+  </si>
+  <si>
+    <t>7b0b0c509d3e4bee923f6535a0ef2ebd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upstream application payload </t>
+  </si>
+  <si>
+    <t>Reltio</t>
+  </si>
+  <si>
+    <t>sailpoint.thunderbolt.service.IdentityService</t>
+  </si>
+  <si>
+    <t>Guest User B2B</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +116,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,12 +147,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +503,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0805629E-0AD9-4082-B00E-FC29E7855477}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="31.6328125" customWidth="1"/>
+    <col min="2" max="2" width="40.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>